--- a/create_forecast_basic/future/bau/Intermediates/240703_pop_2035_bau.xlsx
+++ b/create_forecast_basic/future/bau/Intermediates/240703_pop_2035_bau.xlsx
@@ -5356,7 +5356,7 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>1305.974585938328</v>
+        <v>1305.974585938327</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>4028.782627877677</v>
+        <v>4028.782627877679</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>3562.081315264884</v>
+        <v>3562.081315264888</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>16419.26684392742</v>
+        <v>16419.26684392741</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>9312.126350879285</v>
+        <v>9312.126350879276</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>16006.67179520546</v>
+        <v>16006.67179520547</v>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>41206.29972442903</v>
+        <v>41206.29972442905</v>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>30462.1319028655</v>
+        <v>30462.13190286547</v>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>1585.408676631027</v>
+        <v>1585.408676631028</v>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
-        <v>7767.603761855494</v>
+        <v>7767.603761855496</v>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>2702.024811113267</v>
+        <v>2702.024811113268</v>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
-        <v>2450.64542921387</v>
+        <v>2450.645429213871</v>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>14002.77330770879</v>
+        <v>14002.77330770878</v>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>10819.42785266067</v>
+        <v>10819.42785266068</v>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
-        <v>3302.325848307276</v>
+        <v>3302.325848307274</v>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>8200.609707374831</v>
+        <v>8200.609707374817</v>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>7565.147748078311</v>
+        <v>7565.147748078309</v>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="n">
-        <v>38873.11194436985</v>
+        <v>38873.11194436986</v>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="n">
-        <v>13126.65879021465</v>
+        <v>13126.65879021464</v>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>28192.43851853586</v>
+        <v>28192.43851853588</v>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
-        <v>6554.221491286947</v>
+        <v>6554.22149128695</v>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
-        <v>5523.962508373967</v>
+        <v>5523.962508373966</v>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
-        <v>4334.755869961611</v>
+        <v>4334.75586996161</v>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
-        <v>684.6527888032921</v>
+        <v>684.6527888032919</v>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
-        <v>3908.982478132856</v>
+        <v>3908.982478132858</v>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="n">
-        <v>2572.230104784569</v>
+        <v>2572.230104784568</v>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
-        <v>4365.397230679947</v>
+        <v>4365.397230679948</v>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
-        <v>7393.24624400836</v>
+        <v>7393.246244008358</v>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
-        <v>3662.288839226992</v>
+        <v>3662.288839226994</v>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
-        <v>2930.350637406753</v>
+        <v>2930.350637406752</v>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
-        <v>4539.438985356734</v>
+        <v>4539.438985356735</v>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
-        <v>5076.454608832668</v>
+        <v>5076.454608832667</v>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
-        <v>5825.420035261761</v>
+        <v>5825.420035261763</v>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="n">
-        <v>8630.795795887614</v>
+        <v>8630.79579588761</v>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
-        <v>6044.051117713002</v>
+        <v>6044.051117713</v>
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr"/>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
-        <v>7559.63023348912</v>
+        <v>7559.630233489119</v>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
-        <v>52732.69591313533</v>
+        <v>52732.69591313535</v>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
-        <v>45708.33911629152</v>
+        <v>45708.33911629151</v>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="n">
-        <v>49714.81691500927</v>
+        <v>49714.81691500924</v>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="n">
-        <v>53157.45913484146</v>
+        <v>53157.45913484147</v>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="n">
-        <v>80779.67991782594</v>
+        <v>80779.67991782588</v>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="n">
-        <v>1787.11255294667</v>
+        <v>1787.112552946668</v>
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="n">
-        <v>14647.17629002616</v>
+        <v>14647.17629002615</v>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr"/>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="n">
-        <v>8663.070694855525</v>
+        <v>8663.070694855527</v>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="n">
-        <v>8448.017542794336</v>
+        <v>8448.01754279434</v>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr"/>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="n">
-        <v>3175.695756748316</v>
+        <v>3175.695756748315</v>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="n">
-        <v>4201.549920323966</v>
+        <v>4201.549920323968</v>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr"/>
@@ -7731,7 +7731,7 @@
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="n">
-        <v>13815.14310002785</v>
+        <v>13815.14310002784</v>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr"/>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="B191" t="inlineStr"/>
       <c r="C191" t="n">
-        <v>4982.525302121554</v>
+        <v>4982.525302121555</v>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="B193" t="inlineStr"/>
       <c r="C193" t="n">
-        <v>27032.57758342853</v>
+        <v>27032.57758342851</v>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
-        <v>16652.35572945489</v>
+        <v>16652.35572945491</v>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
-        <v>67633.45126126515</v>
+        <v>67633.4512612652</v>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="n">
-        <v>12393.11849784211</v>
+        <v>12393.1184978421</v>
       </c>
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr"/>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="n">
-        <v>9967.999733110724</v>
+        <v>9967.999733110726</v>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="n">
-        <v>23143.56242283758</v>
+        <v>23143.56242283759</v>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="n">
-        <v>28991.79303543044</v>
+        <v>28991.79303543042</v>
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="n">
-        <v>40571.91219589894</v>
+        <v>40571.91219589896</v>
       </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr"/>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="n">
-        <v>8456.497692722585</v>
+        <v>8456.497692722587</v>
       </c>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr"/>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="n">
-        <v>6750.274370696202</v>
+        <v>6750.2743706962</v>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="B213" t="inlineStr"/>
       <c r="C213" t="n">
-        <v>3568.500113139339</v>
+        <v>3568.50011313934</v>
       </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr"/>
@@ -8406,7 +8406,7 @@
       </c>
       <c r="B215" t="inlineStr"/>
       <c r="C215" t="n">
-        <v>10791.73007268058</v>
+        <v>10791.73007268057</v>
       </c>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr"/>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="n">
-        <v>4027.039461055915</v>
+        <v>4027.039461055916</v>
       </c>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
@@ -8456,7 +8456,7 @@
       </c>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="n">
-        <v>4847.435309741913</v>
+        <v>4847.435309741912</v>
       </c>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="n">
-        <v>10503.43690607538</v>
+        <v>10503.43690607537</v>
       </c>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="n">
-        <v>9078.117541041664</v>
+        <v>9078.117541041662</v>
       </c>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr"/>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="n">
-        <v>82514.53891390913</v>
+        <v>82514.53891390911</v>
       </c>
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr"/>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="n">
-        <v>12981.32504560365</v>
+        <v>12981.32504560363</v>
       </c>
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr"/>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="n">
-        <v>7292.747889286994</v>
+        <v>7292.747889286991</v>
       </c>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="n">
-        <v>44448.3346440408</v>
+        <v>44448.33464404079</v>
       </c>
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="n">
-        <v>45832.75476262382</v>
+        <v>45832.75476262381</v>
       </c>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="B242" t="inlineStr"/>
       <c r="C242" t="n">
-        <v>31424.24010823533</v>
+        <v>31424.24010823532</v>
       </c>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
@@ -9131,7 +9131,7 @@
       </c>
       <c r="B244" t="inlineStr"/>
       <c r="C244" t="n">
-        <v>43460.86499922544</v>
+        <v>43460.86499922549</v>
       </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr"/>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="B249" t="inlineStr"/>
       <c r="C249" t="n">
-        <v>32247.1773569865</v>
+        <v>32247.17735698649</v>
       </c>
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr"/>
